--- a/pz4/Земляник - Диаграмма Ганта.xlsx
+++ b/pz4/Земляник - Диаграмма Ганта.xlsx
@@ -4361,9 +4361,7 @@
       </c>
     </row>
     <row r="23" spans="2:12" ht="21" x14ac:dyDescent="0.25">
-      <c r="B23" s="33">
-        <v>16</v>
-      </c>
+      <c r="B23" s="33"/>
       <c r="C23" s="34"/>
       <c r="D23" s="35"/>
       <c r="E23" s="35"/>
@@ -4376,9 +4374,7 @@
       <c r="L23" s="48"/>
     </row>
     <row r="24" spans="2:12" ht="21" x14ac:dyDescent="0.25">
-      <c r="B24" s="33">
-        <v>17</v>
-      </c>
+      <c r="B24" s="33"/>
       <c r="C24" s="34"/>
       <c r="D24" s="35"/>
       <c r="E24" s="35"/>
@@ -4391,9 +4387,7 @@
       <c r="L24" s="48"/>
     </row>
     <row r="25" spans="2:12" ht="21" x14ac:dyDescent="0.25">
-      <c r="B25" s="33">
-        <v>18</v>
-      </c>
+      <c r="B25" s="33"/>
       <c r="C25" s="34"/>
       <c r="D25" s="35"/>
       <c r="E25" s="35"/>
@@ -4406,9 +4400,7 @@
       <c r="L25" s="48"/>
     </row>
     <row r="26" spans="2:12" ht="21" x14ac:dyDescent="0.25">
-      <c r="B26" s="33">
-        <v>19</v>
-      </c>
+      <c r="B26" s="33"/>
       <c r="C26" s="34"/>
       <c r="D26" s="35"/>
       <c r="E26" s="35"/>
@@ -4421,9 +4413,7 @@
       <c r="L26" s="48"/>
     </row>
     <row r="27" spans="2:12" ht="21" x14ac:dyDescent="0.25">
-      <c r="B27" s="33">
-        <v>20</v>
-      </c>
+      <c r="B27" s="33"/>
       <c r="C27" s="34"/>
       <c r="D27" s="35"/>
       <c r="E27" s="35"/>
@@ -4436,9 +4426,7 @@
       <c r="L27" s="48"/>
     </row>
     <row r="28" spans="2:12" ht="21" x14ac:dyDescent="0.25">
-      <c r="B28" s="33">
-        <v>21</v>
-      </c>
+      <c r="B28" s="33"/>
       <c r="C28" s="34"/>
       <c r="D28" s="35"/>
       <c r="E28" s="35"/>

--- a/pz4/Земляник - Диаграмма Ганта.xlsx
+++ b/pz4/Земляник - Диаграмма Ганта.xlsx
@@ -4438,7 +4438,6 @@
       <c r="K28" s="47"/>
       <c r="L28" s="48"/>
     </row>
-    <row r="32" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="30" spans="2:12">
       <c r="C30" t="inlineStr">
         <is>
@@ -4453,6 +4452,7 @@
         </is>
       </c>
     </row>
+    <row r="32" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="33" spans="3:6" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C33" s="83" t="s">
         <v>177</v>
@@ -4603,7 +4603,8 @@
   <dimension ref="A1:BQ30"/>
   <sheetFormatPr defaultColWidth="2.75" defaultRowHeight="30" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="2.625" customWidth="1"/>
+    <col min="1" max="1" width="2.625" customWidth="1"/>
+    <col min="2" max="2" width="4.625" customWidth="1"/>
     <col min="3" max="6" width="19.25" customWidth="1"/>
     <col min="7" max="7" width="15.625" style="1" customWidth="1"/>
     <col min="8" max="8" width="13.5" style="1" customWidth="1"/>
